--- a/Ecommerce_Unclean_Project.xlsx
+++ b/Ecommerce_Unclean_Project.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Excel Cleaning New Raw Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytic\Data-Analytics-Portfolio-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABF132F-0B19-499F-8121-639F7702CB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501D1F4A-EE08-48DA-901E-2C672F567DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ecommerce_Unclean" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6690" uniqueCount="1646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7045" uniqueCount="1673">
   <si>
     <t>Order_ID</t>
   </si>
@@ -4958,6 +4958,87 @@
   </si>
   <si>
     <t>ORD1612</t>
+  </si>
+  <si>
+    <t>ORD16013</t>
+  </si>
+  <si>
+    <t>ORD16014</t>
+  </si>
+  <si>
+    <t>ORD16015</t>
+  </si>
+  <si>
+    <t>ORD16016</t>
+  </si>
+  <si>
+    <t>ORD16017</t>
+  </si>
+  <si>
+    <t>ORD16018</t>
+  </si>
+  <si>
+    <t>ORD16019</t>
+  </si>
+  <si>
+    <t>ORD16020</t>
+  </si>
+  <si>
+    <t>ORD16021</t>
+  </si>
+  <si>
+    <t>ORD16022</t>
+  </si>
+  <si>
+    <t>ORD16023</t>
+  </si>
+  <si>
+    <t>ORD16024</t>
+  </si>
+  <si>
+    <t>ORD16025</t>
+  </si>
+  <si>
+    <t>ORD16026</t>
+  </si>
+  <si>
+    <t>ORD16027</t>
+  </si>
+  <si>
+    <t>ORD16028</t>
+  </si>
+  <si>
+    <t>ORD16029</t>
+  </si>
+  <si>
+    <t>ORD16030</t>
+  </si>
+  <si>
+    <t>ORD16031</t>
+  </si>
+  <si>
+    <t>ORD16032</t>
+  </si>
+  <si>
+    <t>ORD16033</t>
+  </si>
+  <si>
+    <t>ORD16034</t>
+  </si>
+  <si>
+    <t>ORD16035</t>
+  </si>
+  <si>
+    <t>ORD16036</t>
+  </si>
+  <si>
+    <t>ORD16037</t>
+  </si>
+  <si>
+    <t>ORD16038</t>
+  </si>
+  <si>
+    <t>ORD16039</t>
   </si>
 </sst>
 </file>
@@ -5303,27 +5384,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O525"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O552"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5370,7 +5451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -5417,7 +5498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -5464,7 +5545,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -5511,7 +5592,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -5558,7 +5639,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -5605,7 +5686,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -5652,7 +5733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -5699,7 +5780,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -5746,7 +5827,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -5793,7 +5874,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -5840,7 +5921,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -5887,7 +5968,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>109</v>
       </c>
@@ -5934,7 +6015,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -5981,7 +6062,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -6028,7 +6109,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>123</v>
       </c>
@@ -6075,7 +6156,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -6122,7 +6203,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -6169,7 +6250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>139</v>
       </c>
@@ -6216,7 +6297,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -6263,7 +6344,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>148</v>
       </c>
@@ -6310,7 +6391,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>153</v>
       </c>
@@ -6357,7 +6438,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>157</v>
       </c>
@@ -6404,7 +6485,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>162</v>
       </c>
@@ -6451,7 +6532,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>167</v>
       </c>
@@ -6495,7 +6576,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -6542,7 +6623,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>175</v>
       </c>
@@ -6589,7 +6670,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>181</v>
       </c>
@@ -6636,7 +6717,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>186</v>
       </c>
@@ -6683,7 +6764,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -6730,7 +6811,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>194</v>
       </c>
@@ -6777,7 +6858,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>199</v>
       </c>
@@ -6824,7 +6905,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>204</v>
       </c>
@@ -6871,7 +6952,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>207</v>
       </c>
@@ -6918,7 +6999,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>212</v>
       </c>
@@ -6965,7 +7046,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>216</v>
       </c>
@@ -7012,7 +7093,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -7059,7 +7140,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>227</v>
       </c>
@@ -7106,7 +7187,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>231</v>
       </c>
@@ -7153,7 +7234,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>235</v>
       </c>
@@ -7200,7 +7281,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -7247,7 +7328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>244</v>
       </c>
@@ -7294,7 +7375,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>248</v>
       </c>
@@ -7341,7 +7422,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>252</v>
       </c>
@@ -7388,7 +7469,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>254</v>
       </c>
@@ -7435,7 +7516,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>259</v>
       </c>
@@ -7482,7 +7563,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>263</v>
       </c>
@@ -7529,7 +7610,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>267</v>
       </c>
@@ -7576,7 +7657,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>271</v>
       </c>
@@ -7623,7 +7704,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>276</v>
       </c>
@@ -7667,7 +7748,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>280</v>
       </c>
@@ -7714,7 +7795,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>285</v>
       </c>
@@ -7761,7 +7842,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>289</v>
       </c>
@@ -7808,7 +7889,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>294</v>
       </c>
@@ -7855,7 +7936,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>300</v>
       </c>
@@ -7902,7 +7983,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>303</v>
       </c>
@@ -7949,7 +8030,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>306</v>
       </c>
@@ -7996,7 +8077,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>309</v>
       </c>
@@ -8043,7 +8124,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>313</v>
       </c>
@@ -8090,7 +8171,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>318</v>
       </c>
@@ -8137,7 +8218,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>321</v>
       </c>
@@ -8184,7 +8265,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>324</v>
       </c>
@@ -8231,7 +8312,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -8278,7 +8359,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>333</v>
       </c>
@@ -8325,7 +8406,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>337</v>
       </c>
@@ -8372,7 +8453,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>340</v>
       </c>
@@ -8419,7 +8500,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>344</v>
       </c>
@@ -8466,7 +8547,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>348</v>
       </c>
@@ -8513,7 +8594,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>352</v>
       </c>
@@ -8560,7 +8641,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>356</v>
       </c>
@@ -8607,7 +8688,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>360</v>
       </c>
@@ -8654,7 +8735,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>364</v>
       </c>
@@ -8701,7 +8782,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>69</v>
       </c>
@@ -8748,7 +8829,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>373</v>
       </c>
@@ -8795,7 +8876,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>377</v>
       </c>
@@ -8839,7 +8920,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>381</v>
       </c>
@@ -8886,7 +8967,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>385</v>
       </c>
@@ -8933,7 +9014,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>390</v>
       </c>
@@ -8980,7 +9061,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>394</v>
       </c>
@@ -9027,7 +9108,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>398</v>
       </c>
@@ -9074,7 +9155,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>400</v>
       </c>
@@ -9121,7 +9202,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>405</v>
       </c>
@@ -9168,7 +9249,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>409</v>
       </c>
@@ -9215,7 +9296,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>412</v>
       </c>
@@ -9262,7 +9343,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>415</v>
       </c>
@@ -9309,7 +9390,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>419</v>
       </c>
@@ -9356,7 +9437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>422</v>
       </c>
@@ -9403,7 +9484,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>426</v>
       </c>
@@ -9450,7 +9531,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>429</v>
       </c>
@@ -9497,7 +9578,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>434</v>
       </c>
@@ -9544,7 +9625,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>438</v>
       </c>
@@ -9591,7 +9672,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>441</v>
       </c>
@@ -9638,7 +9719,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>444</v>
       </c>
@@ -9685,7 +9766,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>448</v>
       </c>
@@ -9732,7 +9813,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>452</v>
       </c>
@@ -9779,7 +9860,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>455</v>
       </c>
@@ -9826,7 +9907,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>458</v>
       </c>
@@ -9873,7 +9954,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>461</v>
       </c>
@@ -9920,7 +10001,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>463</v>
       </c>
@@ -9967,7 +10048,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>467</v>
       </c>
@@ -10011,7 +10092,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>470</v>
       </c>
@@ -10058,7 +10139,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>474</v>
       </c>
@@ -10105,7 +10186,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>477</v>
       </c>
@@ -10152,7 +10233,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>480</v>
       </c>
@@ -10199,7 +10280,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>483</v>
       </c>
@@ -10246,7 +10327,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>486</v>
       </c>
@@ -10293,7 +10374,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>489</v>
       </c>
@@ -10340,7 +10421,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>493</v>
       </c>
@@ -10387,7 +10468,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>497</v>
       </c>
@@ -10434,7 +10515,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>501</v>
       </c>
@@ -10481,7 +10562,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>503</v>
       </c>
@@ -10528,7 +10609,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>507</v>
       </c>
@@ -10575,7 +10656,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>510</v>
       </c>
@@ -10622,7 +10703,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>514</v>
       </c>
@@ -10669,7 +10750,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>518</v>
       </c>
@@ -10716,7 +10797,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>522</v>
       </c>
@@ -10763,7 +10844,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>526</v>
       </c>
@@ -10810,7 +10891,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>530</v>
       </c>
@@ -10857,7 +10938,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>534</v>
       </c>
@@ -10904,7 +10985,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>538</v>
       </c>
@@ -10951,7 +11032,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>542</v>
       </c>
@@ -10998,7 +11079,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>545</v>
       </c>
@@ -11045,7 +11126,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>548</v>
       </c>
@@ -11092,7 +11173,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>551</v>
       </c>
@@ -11139,7 +11220,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>554</v>
       </c>
@@ -11183,7 +11264,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>557</v>
       </c>
@@ -11230,7 +11311,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>562</v>
       </c>
@@ -11277,7 +11358,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>566</v>
       </c>
@@ -11324,7 +11405,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>571</v>
       </c>
@@ -11371,7 +11452,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>575</v>
       </c>
@@ -11418,7 +11499,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>578</v>
       </c>
@@ -11465,7 +11546,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>581</v>
       </c>
@@ -11512,7 +11593,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>585</v>
       </c>
@@ -11559,7 +11640,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>589</v>
       </c>
@@ -11606,7 +11687,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>592</v>
       </c>
@@ -11653,7 +11734,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>597</v>
       </c>
@@ -11700,7 +11781,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>600</v>
       </c>
@@ -11747,7 +11828,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>604</v>
       </c>
@@ -11794,7 +11875,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>607</v>
       </c>
@@ -11841,7 +11922,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>610</v>
       </c>
@@ -11888,7 +11969,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>613</v>
       </c>
@@ -11935,7 +12016,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>616</v>
       </c>
@@ -11982,7 +12063,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>619</v>
       </c>
@@ -12029,7 +12110,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>623</v>
       </c>
@@ -12076,7 +12157,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>627</v>
       </c>
@@ -12123,7 +12204,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>69</v>
       </c>
@@ -12170,7 +12251,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>632</v>
       </c>
@@ -12217,7 +12298,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>635</v>
       </c>
@@ -12264,7 +12345,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>637</v>
       </c>
@@ -12311,7 +12392,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>639</v>
       </c>
@@ -12355,7 +12436,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>643</v>
       </c>
@@ -12402,7 +12483,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>647</v>
       </c>
@@ -12449,7 +12530,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>651</v>
       </c>
@@ -12496,7 +12577,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>656</v>
       </c>
@@ -12543,7 +12624,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>660</v>
       </c>
@@ -12590,7 +12671,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>664</v>
       </c>
@@ -12637,7 +12718,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>667</v>
       </c>
@@ -12684,7 +12765,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>671</v>
       </c>
@@ -12731,7 +12812,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>674</v>
       </c>
@@ -12778,7 +12859,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>678</v>
       </c>
@@ -12825,7 +12906,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>682</v>
       </c>
@@ -12872,7 +12953,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>685</v>
       </c>
@@ -12919,7 +13000,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>689</v>
       </c>
@@ -12966,7 +13047,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>692</v>
       </c>
@@ -13013,7 +13094,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>696</v>
       </c>
@@ -13060,7 +13141,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>700</v>
       </c>
@@ -13107,7 +13188,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>703</v>
       </c>
@@ -13154,7 +13235,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>706</v>
       </c>
@@ -13201,7 +13282,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>709</v>
       </c>
@@ -13248,7 +13329,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>711</v>
       </c>
@@ -13295,7 +13376,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>713</v>
       </c>
@@ -13342,7 +13423,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>717</v>
       </c>
@@ -13389,7 +13470,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>720</v>
       </c>
@@ -13436,7 +13517,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>723</v>
       </c>
@@ -13483,7 +13564,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>726</v>
       </c>
@@ -13527,7 +13608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>729</v>
       </c>
@@ -13574,7 +13655,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>732</v>
       </c>
@@ -13621,7 +13702,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>735</v>
       </c>
@@ -13668,7 +13749,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>738</v>
       </c>
@@ -13715,7 +13796,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>742</v>
       </c>
@@ -13762,7 +13843,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>747</v>
       </c>
@@ -13809,7 +13890,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>749</v>
       </c>
@@ -13856,7 +13937,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>753</v>
       </c>
@@ -13903,7 +13984,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>756</v>
       </c>
@@ -13950,7 +14031,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>759</v>
       </c>
@@ -13997,7 +14078,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>761</v>
       </c>
@@ -14044,7 +14125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>764</v>
       </c>
@@ -14091,7 +14172,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>767</v>
       </c>
@@ -14138,7 +14219,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>770</v>
       </c>
@@ -14185,7 +14266,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>774</v>
       </c>
@@ -14232,7 +14313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>778</v>
       </c>
@@ -14279,7 +14360,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>781</v>
       </c>
@@ -14326,7 +14407,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>785</v>
       </c>
@@ -14373,7 +14454,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>789</v>
       </c>
@@ -14420,7 +14501,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>792</v>
       </c>
@@ -14467,7 +14548,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>795</v>
       </c>
@@ -14514,7 +14595,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>798</v>
       </c>
@@ -14561,7 +14642,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>801</v>
       </c>
@@ -14608,7 +14689,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>803</v>
       </c>
@@ -14655,7 +14736,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>806</v>
       </c>
@@ -14699,7 +14780,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>809</v>
       </c>
@@ -14746,7 +14827,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>812</v>
       </c>
@@ -14793,7 +14874,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>815</v>
       </c>
@@ -14840,7 +14921,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>818</v>
       </c>
@@ -14887,7 +14968,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>821</v>
       </c>
@@ -14934,7 +15015,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>824</v>
       </c>
@@ -14981,7 +15062,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>828</v>
       </c>
@@ -15028,7 +15109,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>832</v>
       </c>
@@ -15075,7 +15156,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>835</v>
       </c>
@@ -15122,7 +15203,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>839</v>
       </c>
@@ -15169,7 +15250,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>843</v>
       </c>
@@ -15216,7 +15297,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>846</v>
       </c>
@@ -15263,7 +15344,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>849</v>
       </c>
@@ -15310,7 +15391,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>852</v>
       </c>
@@ -15357,7 +15438,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>855</v>
       </c>
@@ -15404,7 +15485,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>858</v>
       </c>
@@ -15451,7 +15532,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>863</v>
       </c>
@@ -15498,7 +15579,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>866</v>
       </c>
@@ -15545,7 +15626,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>69</v>
       </c>
@@ -15592,7 +15673,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>871</v>
       </c>
@@ -15639,7 +15720,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>872</v>
       </c>
@@ -15686,7 +15767,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>875</v>
       </c>
@@ -15733,7 +15814,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>877</v>
       </c>
@@ -15780,7 +15861,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>880</v>
       </c>
@@ -15827,7 +15908,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>882</v>
       </c>
@@ -15871,7 +15952,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>885</v>
       </c>
@@ -15918,7 +15999,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>889</v>
       </c>
@@ -15965,7 +16046,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>891</v>
       </c>
@@ -16012,7 +16093,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>894</v>
       </c>
@@ -16059,7 +16140,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>898</v>
       </c>
@@ -16106,7 +16187,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>901</v>
       </c>
@@ -16153,7 +16234,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>904</v>
       </c>
@@ -16200,7 +16281,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>906</v>
       </c>
@@ -16247,7 +16328,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>908</v>
       </c>
@@ -16294,7 +16375,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>911</v>
       </c>
@@ -16341,7 +16422,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>914</v>
       </c>
@@ -16388,7 +16469,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>916</v>
       </c>
@@ -16435,7 +16516,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>918</v>
       </c>
@@ -16482,7 +16563,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>921</v>
       </c>
@@ -16529,7 +16610,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>924</v>
       </c>
@@ -16576,7 +16657,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>927</v>
       </c>
@@ -16623,7 +16704,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>930</v>
       </c>
@@ -16670,7 +16751,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>931</v>
       </c>
@@ -16717,7 +16798,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>934</v>
       </c>
@@ -16764,7 +16845,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>937</v>
       </c>
@@ -16811,7 +16892,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>939</v>
       </c>
@@ -16858,7 +16939,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>942</v>
       </c>
@@ -16905,7 +16986,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>944</v>
       </c>
@@ -16952,7 +17033,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>947</v>
       </c>
@@ -16999,7 +17080,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>950</v>
       </c>
@@ -17043,7 +17124,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>952</v>
       </c>
@@ -17090,7 +17171,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>955</v>
       </c>
@@ -17137,7 +17218,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>958</v>
       </c>
@@ -17184,7 +17265,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>961</v>
       </c>
@@ -17231,7 +17312,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>964</v>
       </c>
@@ -17278,7 +17359,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>967</v>
       </c>
@@ -17325,7 +17406,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>969</v>
       </c>
@@ -17372,7 +17453,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>972</v>
       </c>
@@ -17419,7 +17500,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>975</v>
       </c>
@@ -17466,7 +17547,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>978</v>
       </c>
@@ -17513,7 +17594,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>980</v>
       </c>
@@ -17560,7 +17641,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>983</v>
       </c>
@@ -17607,7 +17688,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>986</v>
       </c>
@@ -17654,7 +17735,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>989</v>
       </c>
@@ -17701,7 +17782,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>991</v>
       </c>
@@ -17748,7 +17829,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>994</v>
       </c>
@@ -17795,7 +17876,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>997</v>
       </c>
@@ -17842,7 +17923,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>1001</v>
       </c>
@@ -17889,7 +17970,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>1004</v>
       </c>
@@ -17936,7 +18017,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>1007</v>
       </c>
@@ -17983,7 +18064,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>1011</v>
       </c>
@@ -18030,7 +18111,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>1013</v>
       </c>
@@ -18077,7 +18158,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>1016</v>
       </c>
@@ -18124,7 +18205,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>1020</v>
       </c>
@@ -18171,7 +18252,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>1023</v>
       </c>
@@ -18215,7 +18296,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1026</v>
       </c>
@@ -18262,7 +18343,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1029</v>
       </c>
@@ -18309,7 +18390,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1032</v>
       </c>
@@ -18356,7 +18437,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>1035</v>
       </c>
@@ -18403,7 +18484,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>1038</v>
       </c>
@@ -18450,7 +18531,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1040</v>
       </c>
@@ -18497,7 +18578,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1042</v>
       </c>
@@ -18544,7 +18625,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1045</v>
       </c>
@@ -18591,7 +18672,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>1047</v>
       </c>
@@ -18638,7 +18719,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>1050</v>
       </c>
@@ -18685,7 +18766,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>1052</v>
       </c>
@@ -18732,7 +18813,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>1053</v>
       </c>
@@ -18779,7 +18860,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>1055</v>
       </c>
@@ -18826,7 +18907,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>1058</v>
       </c>
@@ -18873,7 +18954,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>1061</v>
       </c>
@@ -18920,7 +19001,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>1064</v>
       </c>
@@ -18967,7 +19048,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>69</v>
       </c>
@@ -19014,7 +19095,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>1069</v>
       </c>
@@ -19061,7 +19142,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>1072</v>
       </c>
@@ -19108,7 +19189,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>1075</v>
       </c>
@@ -19155,7 +19236,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>1077</v>
       </c>
@@ -19202,7 +19283,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>1080</v>
       </c>
@@ -19249,7 +19330,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>1084</v>
       </c>
@@ -19296,7 +19377,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>1086</v>
       </c>
@@ -19343,7 +19424,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>1089</v>
       </c>
@@ -19387,7 +19468,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>1092</v>
       </c>
@@ -19434,7 +19515,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>1095</v>
       </c>
@@ -19481,7 +19562,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>1098</v>
       </c>
@@ -19528,7 +19609,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>1101</v>
       </c>
@@ -19575,7 +19656,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>1104</v>
       </c>
@@ -19622,7 +19703,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>1107</v>
       </c>
@@ -19669,7 +19750,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>1111</v>
       </c>
@@ -19716,7 +19797,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>1114</v>
       </c>
@@ -19763,7 +19844,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>1115</v>
       </c>
@@ -19810,7 +19891,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>1117</v>
       </c>
@@ -19857,7 +19938,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>1120</v>
       </c>
@@ -19904,7 +19985,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>1123</v>
       </c>
@@ -19951,7 +20032,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>1125</v>
       </c>
@@ -19998,7 +20079,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>1127</v>
       </c>
@@ -20045,7 +20126,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>1129</v>
       </c>
@@ -20092,7 +20173,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>1134</v>
       </c>
@@ -20139,7 +20220,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>1136</v>
       </c>
@@ -20186,7 +20267,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>1138</v>
       </c>
@@ -20233,7 +20314,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>1141</v>
       </c>
@@ -20280,7 +20361,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>1143</v>
       </c>
@@ -20327,7 +20408,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>1146</v>
       </c>
@@ -20374,7 +20455,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>1149</v>
       </c>
@@ -20421,7 +20502,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>1152</v>
       </c>
@@ -20468,7 +20549,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>1155</v>
       </c>
@@ -20515,7 +20596,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>1160</v>
       </c>
@@ -20559,7 +20640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>1163</v>
       </c>
@@ -20606,7 +20687,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>1167</v>
       </c>
@@ -20653,7 +20734,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>1169</v>
       </c>
@@ -20700,7 +20781,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>1172</v>
       </c>
@@ -20747,7 +20828,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>1174</v>
       </c>
@@ -20794,7 +20875,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>1176</v>
       </c>
@@ -20841,7 +20922,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>1178</v>
       </c>
@@ -20888,7 +20969,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>1180</v>
       </c>
@@ -20935,7 +21016,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>1185</v>
       </c>
@@ -20982,7 +21063,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>1188</v>
       </c>
@@ -21029,7 +21110,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>1191</v>
       </c>
@@ -21076,7 +21157,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>1195</v>
       </c>
@@ -21123,7 +21204,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>1198</v>
       </c>
@@ -21170,7 +21251,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>1200</v>
       </c>
@@ -21217,7 +21298,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>1203</v>
       </c>
@@ -21264,7 +21345,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>1205</v>
       </c>
@@ -21311,7 +21392,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>1208</v>
       </c>
@@ -21358,7 +21439,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>1212</v>
       </c>
@@ -21405,7 +21486,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>1215</v>
       </c>
@@ -21452,7 +21533,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>1218</v>
       </c>
@@ -21499,7 +21580,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>1221</v>
       </c>
@@ -21546,7 +21627,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>1223</v>
       </c>
@@ -21593,7 +21674,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>1226</v>
       </c>
@@ -21640,7 +21721,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>1229</v>
       </c>
@@ -21687,7 +21768,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>1232</v>
       </c>
@@ -21731,7 +21812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>1234</v>
       </c>
@@ -21778,7 +21859,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>1239</v>
       </c>
@@ -21825,7 +21906,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>1241</v>
       </c>
@@ -21872,7 +21953,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>1245</v>
       </c>
@@ -21919,7 +22000,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>1247</v>
       </c>
@@ -21966,7 +22047,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>1249</v>
       </c>
@@ -22013,7 +22094,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>1252</v>
       </c>
@@ -22060,7 +22141,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>1255</v>
       </c>
@@ -22107,7 +22188,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>1258</v>
       </c>
@@ -22154,7 +22235,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>1260</v>
       </c>
@@ -22201,7 +22282,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>1263</v>
       </c>
@@ -22248,7 +22329,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>1266</v>
       </c>
@@ -22295,7 +22376,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>1269</v>
       </c>
@@ -22342,7 +22423,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>1272</v>
       </c>
@@ -22389,7 +22470,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>69</v>
       </c>
@@ -22436,7 +22517,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>1277</v>
       </c>
@@ -22483,7 +22564,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>1281</v>
       </c>
@@ -22530,7 +22611,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>1283</v>
       </c>
@@ -22577,7 +22658,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>1286</v>
       </c>
@@ -22624,7 +22705,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>1290</v>
       </c>
@@ -22671,7 +22752,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>1293</v>
       </c>
@@ -22718,7 +22799,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>1296</v>
       </c>
@@ -22765,7 +22846,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>1299</v>
       </c>
@@ -22812,7 +22893,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>1301</v>
       </c>
@@ -22859,7 +22940,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>1303</v>
       </c>
@@ -22903,7 +22984,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>1305</v>
       </c>
@@ -22950,7 +23031,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>1308</v>
       </c>
@@ -22997,7 +23078,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>1311</v>
       </c>
@@ -23044,7 +23125,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>1315</v>
       </c>
@@ -23091,7 +23172,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>1317</v>
       </c>
@@ -23138,7 +23219,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>1320</v>
       </c>
@@ -23185,7 +23266,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>1323</v>
       </c>
@@ -23232,7 +23313,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>1325</v>
       </c>
@@ -23279,7 +23360,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>1327</v>
       </c>
@@ -23326,7 +23407,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>1330</v>
       </c>
@@ -23373,7 +23454,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>1332</v>
       </c>
@@ -23420,7 +23501,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>1334</v>
       </c>
@@ -23467,7 +23548,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>1337</v>
       </c>
@@ -23514,7 +23595,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>1340</v>
       </c>
@@ -23561,7 +23642,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>1343</v>
       </c>
@@ -23608,7 +23689,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>1345</v>
       </c>
@@ -23655,7 +23736,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>1348</v>
       </c>
@@ -23702,7 +23783,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>1351</v>
       </c>
@@ -23749,7 +23830,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>1354</v>
       </c>
@@ -23796,7 +23877,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>1357</v>
       </c>
@@ -23843,7 +23924,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>1359</v>
       </c>
@@ -23890,7 +23971,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>1361</v>
       </c>
@@ -23937,7 +24018,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>1364</v>
       </c>
@@ -23984,7 +24065,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>1367</v>
       </c>
@@ -24031,7 +24112,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>1369</v>
       </c>
@@ -24075,7 +24156,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>1372</v>
       </c>
@@ -24122,7 +24203,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>1375</v>
       </c>
@@ -24169,7 +24250,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>1377</v>
       </c>
@@ -24216,7 +24297,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>1380</v>
       </c>
@@ -24263,7 +24344,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>1382</v>
       </c>
@@ -24310,7 +24391,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>1386</v>
       </c>
@@ -24357,7 +24438,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>1389</v>
       </c>
@@ -24404,7 +24485,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>1392</v>
       </c>
@@ -24451,7 +24532,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>1395</v>
       </c>
@@ -24498,7 +24579,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>1398</v>
       </c>
@@ -24545,7 +24626,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>1401</v>
       </c>
@@ -24592,7 +24673,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>1403</v>
       </c>
@@ -24639,7 +24720,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>1407</v>
       </c>
@@ -24686,7 +24767,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>1409</v>
       </c>
@@ -24733,7 +24814,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>1411</v>
       </c>
@@ -24780,7 +24861,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>1413</v>
       </c>
@@ -24827,7 +24908,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>1415</v>
       </c>
@@ -24874,7 +24955,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>1418</v>
       </c>
@@ -24921,7 +25002,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>1420</v>
       </c>
@@ -24968,7 +25049,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>1422</v>
       </c>
@@ -25015,7 +25096,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>1425</v>
       </c>
@@ -25062,7 +25143,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>1428</v>
       </c>
@@ -25109,7 +25190,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>1430</v>
       </c>
@@ -25156,7 +25237,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>1433</v>
       </c>
@@ -25203,7 +25284,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>1436</v>
       </c>
@@ -25247,7 +25328,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>1438</v>
       </c>
@@ -25294,7 +25375,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>1441</v>
       </c>
@@ -25341,7 +25422,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>1444</v>
       </c>
@@ -25388,7 +25469,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>1446</v>
       </c>
@@ -25435,7 +25516,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>1448</v>
       </c>
@@ -25482,7 +25563,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>1451</v>
       </c>
@@ -25529,7 +25610,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>1455</v>
       </c>
@@ -25576,7 +25657,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>1457</v>
       </c>
@@ -25623,7 +25704,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>1460</v>
       </c>
@@ -25670,7 +25751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>1463</v>
       </c>
@@ -25717,7 +25798,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>1465</v>
       </c>
@@ -25764,7 +25845,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>1467</v>
       </c>
@@ -25811,7 +25892,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>69</v>
       </c>
@@ -25858,7 +25939,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>1471</v>
       </c>
@@ -25905,7 +25986,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>1474</v>
       </c>
@@ -25952,7 +26033,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>1475</v>
       </c>
@@ -25999,7 +26080,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>1478</v>
       </c>
@@ -26046,7 +26127,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>1481</v>
       </c>
@@ -26093,7 +26174,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>1483</v>
       </c>
@@ -26140,7 +26221,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>1485</v>
       </c>
@@ -26187,7 +26268,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>1487</v>
       </c>
@@ -26234,7 +26315,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>1490</v>
       </c>
@@ -26281,7 +26362,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>1493</v>
       </c>
@@ -26328,7 +26409,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>1496</v>
       </c>
@@ -26375,7 +26456,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>1499</v>
       </c>
@@ -26419,7 +26500,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>1503</v>
       </c>
@@ -26466,7 +26547,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>1506</v>
       </c>
@@ -26513,7 +26594,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>1508</v>
       </c>
@@ -26560,7 +26641,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>1511</v>
       </c>
@@ -26607,7 +26688,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>1513</v>
       </c>
@@ -26654,7 +26735,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>1515</v>
       </c>
@@ -26701,7 +26782,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>1518</v>
       </c>
@@ -26748,7 +26829,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>1521</v>
       </c>
@@ -26795,7 +26876,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>1524</v>
       </c>
@@ -26842,7 +26923,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>1528</v>
       </c>
@@ -26889,7 +26970,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>1530</v>
       </c>
@@ -26936,7 +27017,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>1532</v>
       </c>
@@ -26983,7 +27064,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>1534</v>
       </c>
@@ -27030,7 +27111,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>1536</v>
       </c>
@@ -27077,7 +27158,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>1539</v>
       </c>
@@ -27124,7 +27205,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>1542</v>
       </c>
@@ -27171,7 +27252,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>1545</v>
       </c>
@@ -27218,7 +27299,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>1547</v>
       </c>
@@ -27265,7 +27346,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>1550</v>
       </c>
@@ -27312,7 +27393,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>1552</v>
       </c>
@@ -27359,7 +27440,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>1556</v>
       </c>
@@ -27406,7 +27487,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>1558</v>
       </c>
@@ -27453,7 +27534,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>1560</v>
       </c>
@@ -27500,7 +27581,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>1563</v>
       </c>
@@ -27547,7 +27628,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>1566</v>
       </c>
@@ -27591,7 +27672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>1569</v>
       </c>
@@ -27638,7 +27719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>1572</v>
       </c>
@@ -27685,7 +27766,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>1575</v>
       </c>
@@ -27732,7 +27813,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>1578</v>
       </c>
@@ -27779,7 +27860,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>1580</v>
       </c>
@@ -27826,7 +27907,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>1583</v>
       </c>
@@ -27873,7 +27954,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>1586</v>
       </c>
@@ -27920,7 +28001,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>1588</v>
       </c>
@@ -27967,7 +28048,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>1591</v>
       </c>
@@ -28014,7 +28095,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>1592</v>
       </c>
@@ -28061,7 +28142,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>1594</v>
       </c>
@@ -28108,7 +28189,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>1596</v>
       </c>
@@ -28155,7 +28236,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>1598</v>
       </c>
@@ -28202,7 +28283,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>1600</v>
       </c>
@@ -28249,7 +28330,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>1602</v>
       </c>
@@ -28296,7 +28377,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>1604</v>
       </c>
@@ -28343,7 +28424,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>1607</v>
       </c>
@@ -28390,7 +28471,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>1609</v>
       </c>
@@ -28437,7 +28518,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>1611</v>
       </c>
@@ -28484,7 +28565,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>1613</v>
       </c>
@@ -28531,7 +28612,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>1617</v>
       </c>
@@ -28578,7 +28659,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>1620</v>
       </c>
@@ -28625,7 +28706,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>1622</v>
       </c>
@@ -28672,7 +28753,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>1624</v>
       </c>
@@ -28719,7 +28800,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>1627</v>
       </c>
@@ -28763,7 +28844,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>1630</v>
       </c>
@@ -28810,7 +28891,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>15</v>
       </c>
@@ -28857,7 +28938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>28</v>
       </c>
@@ -28904,7 +28985,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>40</v>
       </c>
@@ -28951,7 +29032,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>52</v>
       </c>
@@ -28998,7 +29079,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>63</v>
       </c>
@@ -29045,7 +29126,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>72</v>
       </c>
@@ -29092,7 +29173,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>79</v>
       </c>
@@ -29139,7 +29220,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>86</v>
       </c>
@@ -29186,7 +29267,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>91</v>
       </c>
@@ -29233,7 +29314,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>98</v>
       </c>
@@ -29280,7 +29361,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>103</v>
       </c>
@@ -29327,7 +29408,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>1633</v>
       </c>
@@ -29371,7 +29452,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>1634</v>
       </c>
@@ -29418,7 +29499,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>1635</v>
       </c>
@@ -29465,7 +29546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>1636</v>
       </c>
@@ -29512,7 +29593,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>1637</v>
       </c>
@@ -29559,7 +29640,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>1638</v>
       </c>
@@ -29606,7 +29687,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>1639</v>
       </c>
@@ -29653,7 +29734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>1640</v>
       </c>
@@ -29700,7 +29781,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>1641</v>
       </c>
@@ -29747,7 +29828,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>1642</v>
       </c>
@@ -29794,7 +29875,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>1643</v>
       </c>
@@ -29841,7 +29922,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>1644</v>
       </c>
@@ -29888,7 +29969,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>1645</v>
       </c>
@@ -29932,6 +30013,1275 @@
         <v>70</v>
       </c>
       <c r="O525" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B526" t="s">
+        <v>659</v>
+      </c>
+      <c r="C526" t="s">
+        <v>42</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E526" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F526" t="s">
+        <v>83</v>
+      </c>
+      <c r="G526" t="s">
+        <v>84</v>
+      </c>
+      <c r="H526" t="s">
+        <v>21</v>
+      </c>
+      <c r="I526" t="s">
+        <v>22</v>
+      </c>
+      <c r="J526">
+        <v>-1</v>
+      </c>
+      <c r="K526">
+        <v>1499</v>
+      </c>
+      <c r="L526">
+        <v>15</v>
+      </c>
+      <c r="M526" t="s">
+        <v>61</v>
+      </c>
+      <c r="N526" t="s">
+        <v>96</v>
+      </c>
+      <c r="O526" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B527" t="s">
+        <v>16</v>
+      </c>
+      <c r="C527" t="s">
+        <v>17</v>
+      </c>
+      <c r="D527" t="s">
+        <v>18</v>
+      </c>
+      <c r="E527" t="s">
+        <v>19</v>
+      </c>
+      <c r="F527" t="s">
+        <v>20</v>
+      </c>
+      <c r="G527" t="s">
+        <v>20</v>
+      </c>
+      <c r="H527" t="s">
+        <v>21</v>
+      </c>
+      <c r="I527" t="s">
+        <v>22</v>
+      </c>
+      <c r="J527">
+        <v>4</v>
+      </c>
+      <c r="K527" t="s">
+        <v>23</v>
+      </c>
+      <c r="L527" t="s">
+        <v>24</v>
+      </c>
+      <c r="M527" t="s">
+        <v>25</v>
+      </c>
+      <c r="N527" t="s">
+        <v>26</v>
+      </c>
+      <c r="O527" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B528" t="s">
+        <v>29</v>
+      </c>
+      <c r="C528" t="s">
+        <v>30</v>
+      </c>
+      <c r="D528" t="s">
+        <v>31</v>
+      </c>
+      <c r="E528" t="s">
+        <v>32</v>
+      </c>
+      <c r="F528" t="s">
+        <v>33</v>
+      </c>
+      <c r="G528" t="s">
+        <v>34</v>
+      </c>
+      <c r="H528" t="s">
+        <v>35</v>
+      </c>
+      <c r="I528" t="s">
+        <v>36</v>
+      </c>
+      <c r="J528" t="s">
+        <v>37</v>
+      </c>
+      <c r="K528">
+        <v>4999</v>
+      </c>
+      <c r="L528">
+        <v>20</v>
+      </c>
+      <c r="M528" t="s">
+        <v>38</v>
+      </c>
+      <c r="N528" t="s">
+        <v>26</v>
+      </c>
+      <c r="O528" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B529" t="s">
+        <v>41</v>
+      </c>
+      <c r="C529" t="s">
+        <v>42</v>
+      </c>
+      <c r="D529" t="s">
+        <v>43</v>
+      </c>
+      <c r="E529" t="s">
+        <v>44</v>
+      </c>
+      <c r="F529" t="s">
+        <v>45</v>
+      </c>
+      <c r="G529" t="s">
+        <v>46</v>
+      </c>
+      <c r="H529" t="s">
+        <v>47</v>
+      </c>
+      <c r="I529" t="s">
+        <v>48</v>
+      </c>
+      <c r="J529">
+        <v>3</v>
+      </c>
+      <c r="K529" t="s">
+        <v>23</v>
+      </c>
+      <c r="L529">
+        <v>5</v>
+      </c>
+      <c r="M529" t="s">
+        <v>49</v>
+      </c>
+      <c r="N529" t="s">
+        <v>50</v>
+      </c>
+      <c r="O529" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B530" t="s">
+        <v>53</v>
+      </c>
+      <c r="C530" t="s">
+        <v>54</v>
+      </c>
+      <c r="D530" t="s">
+        <v>55</v>
+      </c>
+      <c r="E530" t="s">
+        <v>56</v>
+      </c>
+      <c r="F530" t="s">
+        <v>57</v>
+      </c>
+      <c r="G530" t="s">
+        <v>58</v>
+      </c>
+      <c r="H530" t="s">
+        <v>59</v>
+      </c>
+      <c r="I530" t="s">
+        <v>48</v>
+      </c>
+      <c r="J530" t="s">
+        <v>24</v>
+      </c>
+      <c r="K530" t="s">
+        <v>60</v>
+      </c>
+      <c r="L530">
+        <v>15</v>
+      </c>
+      <c r="M530" t="s">
+        <v>61</v>
+      </c>
+      <c r="N530" t="s">
+        <v>26</v>
+      </c>
+      <c r="O530" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B531" t="s">
+        <v>64</v>
+      </c>
+      <c r="C531" t="s">
+        <v>30</v>
+      </c>
+      <c r="D531" t="s">
+        <v>65</v>
+      </c>
+      <c r="E531" t="s">
+        <v>66</v>
+      </c>
+      <c r="F531" t="s">
+        <v>33</v>
+      </c>
+      <c r="G531" t="s">
+        <v>34</v>
+      </c>
+      <c r="H531" t="s">
+        <v>67</v>
+      </c>
+      <c r="I531" t="s">
+        <v>68</v>
+      </c>
+      <c r="J531" t="s">
+        <v>24</v>
+      </c>
+      <c r="K531" t="s">
+        <v>23</v>
+      </c>
+      <c r="L531" t="s">
+        <v>69</v>
+      </c>
+      <c r="M531" t="s">
+        <v>61</v>
+      </c>
+      <c r="N531" t="s">
+        <v>70</v>
+      </c>
+      <c r="O531" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B532" t="s">
+        <v>73</v>
+      </c>
+      <c r="C532" t="s">
+        <v>74</v>
+      </c>
+      <c r="D532" t="s">
+        <v>75</v>
+      </c>
+      <c r="E532" t="s">
+        <v>76</v>
+      </c>
+      <c r="F532" t="s">
+        <v>77</v>
+      </c>
+      <c r="G532" t="s">
+        <v>34</v>
+      </c>
+      <c r="H532" t="s">
+        <v>47</v>
+      </c>
+      <c r="I532" t="s">
+        <v>48</v>
+      </c>
+      <c r="J532">
+        <v>3</v>
+      </c>
+      <c r="K532">
+        <v>499</v>
+      </c>
+      <c r="L532">
+        <v>20</v>
+      </c>
+      <c r="M532" t="s">
+        <v>61</v>
+      </c>
+      <c r="N532" t="s">
+        <v>70</v>
+      </c>
+      <c r="O532" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B533" t="s">
+        <v>80</v>
+      </c>
+      <c r="C533" t="s">
+        <v>74</v>
+      </c>
+      <c r="D533" t="s">
+        <v>81</v>
+      </c>
+      <c r="E533" t="s">
+        <v>82</v>
+      </c>
+      <c r="F533" t="s">
+        <v>83</v>
+      </c>
+      <c r="G533" t="s">
+        <v>84</v>
+      </c>
+      <c r="H533" t="s">
+        <v>47</v>
+      </c>
+      <c r="I533" t="s">
+        <v>48</v>
+      </c>
+      <c r="J533">
+        <v>4</v>
+      </c>
+      <c r="K533">
+        <v>9999</v>
+      </c>
+      <c r="L533" t="s">
+        <v>24</v>
+      </c>
+      <c r="M533" t="s">
+        <v>38</v>
+      </c>
+      <c r="N533" t="s">
+        <v>50</v>
+      </c>
+      <c r="O533" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B534" t="s">
+        <v>87</v>
+      </c>
+      <c r="C534" t="s">
+        <v>74</v>
+      </c>
+      <c r="D534" t="s">
+        <v>88</v>
+      </c>
+      <c r="E534" t="s">
+        <v>89</v>
+      </c>
+      <c r="F534" t="s">
+        <v>77</v>
+      </c>
+      <c r="G534" t="s">
+        <v>34</v>
+      </c>
+      <c r="H534" t="s">
+        <v>67</v>
+      </c>
+      <c r="I534" t="s">
+        <v>68</v>
+      </c>
+      <c r="J534">
+        <v>2</v>
+      </c>
+      <c r="K534">
+        <v>1499</v>
+      </c>
+      <c r="L534" t="s">
+        <v>69</v>
+      </c>
+      <c r="M534" t="s">
+        <v>61</v>
+      </c>
+      <c r="N534" t="s">
+        <v>26</v>
+      </c>
+      <c r="O534" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B535" t="s">
+        <v>92</v>
+      </c>
+      <c r="C535" t="s">
+        <v>30</v>
+      </c>
+      <c r="D535" t="s">
+        <v>93</v>
+      </c>
+      <c r="E535" t="s">
+        <v>94</v>
+      </c>
+      <c r="F535" t="s">
+        <v>45</v>
+      </c>
+      <c r="G535" t="s">
+        <v>46</v>
+      </c>
+      <c r="H535" t="s">
+        <v>47</v>
+      </c>
+      <c r="I535" t="s">
+        <v>48</v>
+      </c>
+      <c r="J535">
+        <v>1</v>
+      </c>
+      <c r="K535" t="s">
+        <v>60</v>
+      </c>
+      <c r="L535" t="s">
+        <v>69</v>
+      </c>
+      <c r="M535" t="s">
+        <v>95</v>
+      </c>
+      <c r="N535" t="s">
+        <v>96</v>
+      </c>
+      <c r="O535" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B536" t="s">
+        <v>99</v>
+      </c>
+      <c r="C536" t="s">
+        <v>17</v>
+      </c>
+      <c r="D536" t="s">
+        <v>100</v>
+      </c>
+      <c r="E536" t="s">
+        <v>101</v>
+      </c>
+      <c r="F536" t="s">
+        <v>45</v>
+      </c>
+      <c r="G536" t="s">
+        <v>46</v>
+      </c>
+      <c r="H536" t="s">
+        <v>21</v>
+      </c>
+      <c r="I536" t="s">
+        <v>22</v>
+      </c>
+      <c r="J536">
+        <v>3</v>
+      </c>
+      <c r="K536">
+        <v>999</v>
+      </c>
+      <c r="L536" t="s">
+        <v>69</v>
+      </c>
+      <c r="M536" t="s">
+        <v>49</v>
+      </c>
+      <c r="N536" t="s">
+        <v>26</v>
+      </c>
+      <c r="O536" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B537" t="s">
+        <v>104</v>
+      </c>
+      <c r="C537" t="s">
+        <v>54</v>
+      </c>
+      <c r="D537" t="s">
+        <v>105</v>
+      </c>
+      <c r="E537" t="s">
+        <v>106</v>
+      </c>
+      <c r="F537" t="s">
+        <v>45</v>
+      </c>
+      <c r="G537" t="s">
+        <v>46</v>
+      </c>
+      <c r="H537" t="s">
+        <v>107</v>
+      </c>
+      <c r="I537" t="s">
+        <v>36</v>
+      </c>
+      <c r="J537">
+        <v>3</v>
+      </c>
+      <c r="K537">
+        <v>999</v>
+      </c>
+      <c r="L537">
+        <v>5</v>
+      </c>
+      <c r="M537" t="s">
+        <v>49</v>
+      </c>
+      <c r="N537" t="s">
+        <v>70</v>
+      </c>
+      <c r="O537" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B538" t="s">
+        <v>92</v>
+      </c>
+      <c r="C538" t="s">
+        <v>30</v>
+      </c>
+      <c r="D538" t="s">
+        <v>93</v>
+      </c>
+      <c r="E538" t="s">
+        <v>94</v>
+      </c>
+      <c r="F538" t="s">
+        <v>45</v>
+      </c>
+      <c r="G538" t="s">
+        <v>46</v>
+      </c>
+      <c r="H538" t="s">
+        <v>47</v>
+      </c>
+      <c r="I538" t="s">
+        <v>48</v>
+      </c>
+      <c r="J538">
+        <v>1</v>
+      </c>
+      <c r="K538" t="s">
+        <v>60</v>
+      </c>
+      <c r="L538" t="s">
+        <v>69</v>
+      </c>
+      <c r="M538" t="s">
+        <v>95</v>
+      </c>
+      <c r="N538" t="s">
+        <v>96</v>
+      </c>
+      <c r="O538" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B539" t="s">
+        <v>99</v>
+      </c>
+      <c r="C539" t="s">
+        <v>17</v>
+      </c>
+      <c r="D539" t="s">
+        <v>100</v>
+      </c>
+      <c r="E539" t="s">
+        <v>101</v>
+      </c>
+      <c r="F539" t="s">
+        <v>45</v>
+      </c>
+      <c r="G539" t="s">
+        <v>46</v>
+      </c>
+      <c r="H539" t="s">
+        <v>21</v>
+      </c>
+      <c r="I539" t="s">
+        <v>22</v>
+      </c>
+      <c r="J539">
+        <v>3</v>
+      </c>
+      <c r="K539">
+        <v>999</v>
+      </c>
+      <c r="L539" t="s">
+        <v>69</v>
+      </c>
+      <c r="M539" t="s">
+        <v>49</v>
+      </c>
+      <c r="N539" t="s">
+        <v>26</v>
+      </c>
+      <c r="O539" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B540" t="s">
+        <v>104</v>
+      </c>
+      <c r="C540" t="s">
+        <v>54</v>
+      </c>
+      <c r="D540" t="s">
+        <v>105</v>
+      </c>
+      <c r="E540" t="s">
+        <v>106</v>
+      </c>
+      <c r="F540" t="s">
+        <v>45</v>
+      </c>
+      <c r="G540" t="s">
+        <v>46</v>
+      </c>
+      <c r="H540" t="s">
+        <v>107</v>
+      </c>
+      <c r="I540" t="s">
+        <v>36</v>
+      </c>
+      <c r="J540">
+        <v>3</v>
+      </c>
+      <c r="K540">
+        <v>999</v>
+      </c>
+      <c r="L540">
+        <v>5</v>
+      </c>
+      <c r="M540" t="s">
+        <v>49</v>
+      </c>
+      <c r="N540" t="s">
+        <v>70</v>
+      </c>
+      <c r="O540" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B541" t="s">
+        <v>659</v>
+      </c>
+      <c r="C541" t="s">
+        <v>42</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E541" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F541" t="s">
+        <v>83</v>
+      </c>
+      <c r="G541" t="s">
+        <v>84</v>
+      </c>
+      <c r="H541" t="s">
+        <v>21</v>
+      </c>
+      <c r="I541" t="s">
+        <v>22</v>
+      </c>
+      <c r="J541">
+        <v>-1</v>
+      </c>
+      <c r="K541">
+        <v>1499</v>
+      </c>
+      <c r="L541">
+        <v>15</v>
+      </c>
+      <c r="M541" t="s">
+        <v>61</v>
+      </c>
+      <c r="N541" t="s">
+        <v>96</v>
+      </c>
+      <c r="O541" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B542" t="s">
+        <v>16</v>
+      </c>
+      <c r="C542" t="s">
+        <v>17</v>
+      </c>
+      <c r="D542" t="s">
+        <v>18</v>
+      </c>
+      <c r="E542" t="s">
+        <v>19</v>
+      </c>
+      <c r="F542" t="s">
+        <v>20</v>
+      </c>
+      <c r="G542" t="s">
+        <v>20</v>
+      </c>
+      <c r="H542" t="s">
+        <v>21</v>
+      </c>
+      <c r="I542" t="s">
+        <v>22</v>
+      </c>
+      <c r="J542">
+        <v>4</v>
+      </c>
+      <c r="K542" t="s">
+        <v>23</v>
+      </c>
+      <c r="L542" t="s">
+        <v>24</v>
+      </c>
+      <c r="M542" t="s">
+        <v>25</v>
+      </c>
+      <c r="N542" t="s">
+        <v>26</v>
+      </c>
+      <c r="O542" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B543" t="s">
+        <v>29</v>
+      </c>
+      <c r="C543" t="s">
+        <v>30</v>
+      </c>
+      <c r="D543" t="s">
+        <v>31</v>
+      </c>
+      <c r="E543" t="s">
+        <v>32</v>
+      </c>
+      <c r="F543" t="s">
+        <v>33</v>
+      </c>
+      <c r="G543" t="s">
+        <v>34</v>
+      </c>
+      <c r="H543" t="s">
+        <v>35</v>
+      </c>
+      <c r="I543" t="s">
+        <v>36</v>
+      </c>
+      <c r="J543" t="s">
+        <v>37</v>
+      </c>
+      <c r="K543">
+        <v>4999</v>
+      </c>
+      <c r="L543">
+        <v>20</v>
+      </c>
+      <c r="M543" t="s">
+        <v>38</v>
+      </c>
+      <c r="N543" t="s">
+        <v>26</v>
+      </c>
+      <c r="O543" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B544" t="s">
+        <v>41</v>
+      </c>
+      <c r="C544" t="s">
+        <v>42</v>
+      </c>
+      <c r="D544" t="s">
+        <v>43</v>
+      </c>
+      <c r="E544" t="s">
+        <v>44</v>
+      </c>
+      <c r="F544" t="s">
+        <v>45</v>
+      </c>
+      <c r="G544" t="s">
+        <v>46</v>
+      </c>
+      <c r="H544" t="s">
+        <v>47</v>
+      </c>
+      <c r="I544" t="s">
+        <v>48</v>
+      </c>
+      <c r="J544">
+        <v>3</v>
+      </c>
+      <c r="K544" t="s">
+        <v>23</v>
+      </c>
+      <c r="L544">
+        <v>5</v>
+      </c>
+      <c r="M544" t="s">
+        <v>49</v>
+      </c>
+      <c r="N544" t="s">
+        <v>50</v>
+      </c>
+      <c r="O544" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B545" t="s">
+        <v>53</v>
+      </c>
+      <c r="C545" t="s">
+        <v>54</v>
+      </c>
+      <c r="D545" t="s">
+        <v>55</v>
+      </c>
+      <c r="E545" t="s">
+        <v>56</v>
+      </c>
+      <c r="F545" t="s">
+        <v>57</v>
+      </c>
+      <c r="G545" t="s">
+        <v>58</v>
+      </c>
+      <c r="H545" t="s">
+        <v>59</v>
+      </c>
+      <c r="I545" t="s">
+        <v>48</v>
+      </c>
+      <c r="J545" t="s">
+        <v>24</v>
+      </c>
+      <c r="K545" t="s">
+        <v>60</v>
+      </c>
+      <c r="L545">
+        <v>15</v>
+      </c>
+      <c r="M545" t="s">
+        <v>61</v>
+      </c>
+      <c r="N545" t="s">
+        <v>26</v>
+      </c>
+      <c r="O545" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B546" t="s">
+        <v>64</v>
+      </c>
+      <c r="C546" t="s">
+        <v>30</v>
+      </c>
+      <c r="D546" t="s">
+        <v>65</v>
+      </c>
+      <c r="E546" t="s">
+        <v>66</v>
+      </c>
+      <c r="F546" t="s">
+        <v>33</v>
+      </c>
+      <c r="G546" t="s">
+        <v>34</v>
+      </c>
+      <c r="H546" t="s">
+        <v>67</v>
+      </c>
+      <c r="I546" t="s">
+        <v>68</v>
+      </c>
+      <c r="J546" t="s">
+        <v>24</v>
+      </c>
+      <c r="K546" t="s">
+        <v>23</v>
+      </c>
+      <c r="L546" t="s">
+        <v>69</v>
+      </c>
+      <c r="M546" t="s">
+        <v>61</v>
+      </c>
+      <c r="N546" t="s">
+        <v>70</v>
+      </c>
+      <c r="O546" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B547" t="s">
+        <v>73</v>
+      </c>
+      <c r="C547" t="s">
+        <v>74</v>
+      </c>
+      <c r="D547" t="s">
+        <v>75</v>
+      </c>
+      <c r="E547" t="s">
+        <v>76</v>
+      </c>
+      <c r="F547" t="s">
+        <v>77</v>
+      </c>
+      <c r="G547" t="s">
+        <v>34</v>
+      </c>
+      <c r="H547" t="s">
+        <v>47</v>
+      </c>
+      <c r="I547" t="s">
+        <v>48</v>
+      </c>
+      <c r="J547">
+        <v>3</v>
+      </c>
+      <c r="K547">
+        <v>499</v>
+      </c>
+      <c r="L547">
+        <v>20</v>
+      </c>
+      <c r="M547" t="s">
+        <v>61</v>
+      </c>
+      <c r="N547" t="s">
+        <v>70</v>
+      </c>
+      <c r="O547" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B548" t="s">
+        <v>80</v>
+      </c>
+      <c r="C548" t="s">
+        <v>74</v>
+      </c>
+      <c r="D548" t="s">
+        <v>81</v>
+      </c>
+      <c r="E548" t="s">
+        <v>82</v>
+      </c>
+      <c r="F548" t="s">
+        <v>83</v>
+      </c>
+      <c r="G548" t="s">
+        <v>84</v>
+      </c>
+      <c r="H548" t="s">
+        <v>47</v>
+      </c>
+      <c r="I548" t="s">
+        <v>48</v>
+      </c>
+      <c r="J548">
+        <v>4</v>
+      </c>
+      <c r="K548">
+        <v>9999</v>
+      </c>
+      <c r="L548" t="s">
+        <v>24</v>
+      </c>
+      <c r="M548" t="s">
+        <v>38</v>
+      </c>
+      <c r="N548" t="s">
+        <v>50</v>
+      </c>
+      <c r="O548" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B549" t="s">
+        <v>87</v>
+      </c>
+      <c r="C549" t="s">
+        <v>74</v>
+      </c>
+      <c r="D549" t="s">
+        <v>88</v>
+      </c>
+      <c r="E549" t="s">
+        <v>89</v>
+      </c>
+      <c r="F549" t="s">
+        <v>77</v>
+      </c>
+      <c r="G549" t="s">
+        <v>34</v>
+      </c>
+      <c r="H549" t="s">
+        <v>67</v>
+      </c>
+      <c r="I549" t="s">
+        <v>68</v>
+      </c>
+      <c r="J549">
+        <v>2</v>
+      </c>
+      <c r="K549">
+        <v>1499</v>
+      </c>
+      <c r="L549" t="s">
+        <v>69</v>
+      </c>
+      <c r="M549" t="s">
+        <v>61</v>
+      </c>
+      <c r="N549" t="s">
+        <v>26</v>
+      </c>
+      <c r="O549" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B550" t="s">
+        <v>92</v>
+      </c>
+      <c r="C550" t="s">
+        <v>30</v>
+      </c>
+      <c r="D550" t="s">
+        <v>93</v>
+      </c>
+      <c r="E550" t="s">
+        <v>94</v>
+      </c>
+      <c r="F550" t="s">
+        <v>45</v>
+      </c>
+      <c r="G550" t="s">
+        <v>46</v>
+      </c>
+      <c r="H550" t="s">
+        <v>47</v>
+      </c>
+      <c r="I550" t="s">
+        <v>48</v>
+      </c>
+      <c r="J550">
+        <v>1</v>
+      </c>
+      <c r="K550" t="s">
+        <v>60</v>
+      </c>
+      <c r="L550" t="s">
+        <v>69</v>
+      </c>
+      <c r="M550" t="s">
+        <v>95</v>
+      </c>
+      <c r="N550" t="s">
+        <v>96</v>
+      </c>
+      <c r="O550" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B551" t="s">
+        <v>99</v>
+      </c>
+      <c r="C551" t="s">
+        <v>17</v>
+      </c>
+      <c r="D551" t="s">
+        <v>100</v>
+      </c>
+      <c r="E551" t="s">
+        <v>101</v>
+      </c>
+      <c r="F551" t="s">
+        <v>45</v>
+      </c>
+      <c r="G551" t="s">
+        <v>46</v>
+      </c>
+      <c r="H551" t="s">
+        <v>21</v>
+      </c>
+      <c r="I551" t="s">
+        <v>22</v>
+      </c>
+      <c r="J551">
+        <v>3</v>
+      </c>
+      <c r="K551">
+        <v>999</v>
+      </c>
+      <c r="L551" t="s">
+        <v>69</v>
+      </c>
+      <c r="M551" t="s">
+        <v>49</v>
+      </c>
+      <c r="N551" t="s">
+        <v>26</v>
+      </c>
+      <c r="O551" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B552" t="s">
+        <v>104</v>
+      </c>
+      <c r="C552" t="s">
+        <v>54</v>
+      </c>
+      <c r="D552" t="s">
+        <v>105</v>
+      </c>
+      <c r="E552" t="s">
+        <v>106</v>
+      </c>
+      <c r="F552" t="s">
+        <v>45</v>
+      </c>
+      <c r="G552" t="s">
+        <v>46</v>
+      </c>
+      <c r="H552" t="s">
+        <v>107</v>
+      </c>
+      <c r="I552" t="s">
+        <v>36</v>
+      </c>
+      <c r="J552">
+        <v>3</v>
+      </c>
+      <c r="K552">
+        <v>999</v>
+      </c>
+      <c r="L552">
+        <v>5</v>
+      </c>
+      <c r="M552" t="s">
+        <v>49</v>
+      </c>
+      <c r="N552" t="s">
+        <v>70</v>
+      </c>
+      <c r="O552" t="s">
         <v>108</v>
       </c>
     </row>

--- a/Ecommerce_Unclean_Project.xlsx
+++ b/Ecommerce_Unclean_Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytic\Data-Analytics-Portfolio-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501D1F4A-EE08-48DA-901E-2C672F567DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC2CEE9-803C-497C-A7F2-6B36B21FBFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
